--- a/liga_eliminacao/datasets_liga_eliminacao/links_times_cartola_liga_eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/links_times_cartola_liga_eliminacao.xlsx
@@ -52,7 +52,7 @@
     <t>PUXE FC</t>
   </si>
   <si>
-    <t>NaoVaiDescer!</t>
+    <t>VaiDescerkkkk!!!</t>
   </si>
   <si>
     <t>cartola scheuer17</t>
